--- a/www/download/IND.gross_output.s.du.EXI382.xlsx
+++ b/www/download/IND.gross_output.s.du.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>166800.210542846</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>211513.626092526</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>219492.619379992</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>245946.081379178</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>301158.271056238</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>363003.893811456</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>385140.363424</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>425998.75209484</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>367663.153299373</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>427085.440598152</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>485623.257061724</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>486374.930441717</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>461816.940453793</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>527688.272636003</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>548486.058018378</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>575827.165940957</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>680969.509138428</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>710721.292143832</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>691380.522201665</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>599665.613215486</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>585475.346351323</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>507206.430814732</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>550377.401634763</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>562281.204379765</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>547487.279319838</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>545309.476108965</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>550335.626740787</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>37526.9039298849</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>68319.8877927701</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>72361.2789897087</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>78316.728159814</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>89298.733618848</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>107588.416669781</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>115936.022396127</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>104169.223169573</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>96805.9964507622</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>99002.460978579</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>108161.227275595</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>115885.968143972</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>115610.085763681</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>125565.038935017</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>117191.880557511</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>141318.139899647</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>160421.067084372</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>181591.862354826</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>173277.947019303</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>156314.368762066</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>171299.356109284</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>156482.783568427</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>162439.152442838</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>175900.849829074</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>192583.870722272</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>192620.808354711</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>190741.845474591</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>85514.0216525486</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>109138.965134249</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>128577.214798974</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>135698.98636073</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>145695.34121925</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>192944.49768293</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>211383.473826694</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>183991.437042651</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>155663.661764324</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>169737.292664786</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>188156.658206267</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>200571.311741477</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>191657.128130147</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>238067.888657068</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>204806.051631641</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>248352.866203677</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>298253.689796818</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>317789.857828066</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>359077.926011796</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>312331.586998865</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>336404.081051603</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>330558.155167285</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>299906.969097284</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>333501.489982084</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>322222.445792918</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>343386.588766883</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>354916.365707967</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>36969.9375855968</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>73056.32062516</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>78883.5660441412</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>73607.9795788076</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>76458.5619648459</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>89996.0262072142</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>81921.0215402314</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>76608.9849362914</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>70710.7174030152</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>77379.4981396798</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>84950.6778237946</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>93147.9492445969</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>100731.648314298</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>111965.649823167</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>107504.872907246</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>108703.442374196</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>111588.897884436</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>118729.504460702</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>112445.611797015</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>165861.346428365</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>177936.355230558</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>179455.169015716</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>176441.902127037</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>185417.896903137</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>213052.638377924</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>209439.515170996</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>175317.788773849</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>602294.504597723</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1161386.52958642</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1233049.47964544</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1244524.95484809</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>1315506.20198263</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1636046.13751304</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1650126.96259507</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1629694.48787303</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1508610.94792337</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1544194.4936896</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1779121.80768239</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1930448.25773977</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1998522.98845968</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.859</t>
+          <t>2104754.59244457</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.767</t>
+          <t>2009264.40164235</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2367540.56302567</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>2475571.24739702</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.351</t>
+          <t>2694722.71870786</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2723757.97105778</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>2623818.23060454</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2788034.48548267</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1.887</t>
+          <t>2214190.64034587</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2.058</t>
+          <t>2430772.54639866</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2526229.59683895</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2403060.62233423</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>2347857.83243925</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1.976</t>
+          <t>2355508.65520871</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>294977.509845218</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>183729.557052098</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>191476.052434578</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>201885.743279252</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>223211.233699295</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>303525.132927072</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>306211.141963916</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>300806.473974457</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>273843.227791191</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>307802.57703969</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>338649.843279917</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>334852.357893839</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>356394.79232769</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>372611.577412724</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>367139.667280775</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>400221.021417722</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>470155.670247203</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>550554.839724654</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>545244.764846862</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>468357.30467842</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>500308.8853203</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>464548.940940255</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>454536.052635406</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>468847.81725943</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>473756.731361838</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>470469.921141671</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>493290.794126508</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12.128</t>
+          <t>12662543.4756209</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.771</t>
+          <t>14915378.8055018</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.202</t>
+          <t>16765844.6186556</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15.243</t>
+          <t>15742904.3421138</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16.646</t>
+          <t>17242466.4172659</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19.474</t>
+          <t>20274156.399772</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.722</t>
+          <t>20515677.4926744</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.387</t>
+          <t>20150096.0963002</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.492</t>
+          <t>19146252.0676544</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19.574</t>
+          <t>20105865.2507496</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>21.609</t>
+          <t>22177011.9144426</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>23.869</t>
+          <t>24442348.1777291</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>25.483</t>
+          <t>26123471.2584072</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24.157</t>
+          <t>24696091.2582725</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>23.754</t>
+          <t>24419885.2693176</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>27.848</t>
+          <t>28673954.1316713</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>30.907</t>
+          <t>31917564.2079512</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>34.427</t>
+          <t>35727368.7249143</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>35.736</t>
+          <t>37250966.0590479</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>39.251</t>
+          <t>41203421.9922845</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>46.531</t>
+          <t>49390441.4684687</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>48.401</t>
+          <t>51733970.4091592</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>51.004</t>
+          <t>54788924.7948837</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>52.045</t>
+          <t>56244573.216777</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>58.175</t>
+          <t>62997382.8750115</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>59.373</t>
+          <t>64390972.5948612</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>61.891</t>
+          <t>67199072.7950901</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4277.32706176845</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7523.06808005066</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7496.30682457825</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7807.77150525458</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9016.85558219547</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10964.0582080262</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12554.7291001555</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>12065.6699892585</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10980.7041721155</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10060.3088507744</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11238.9976216259</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9931.19589617085</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9152.94009143738</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12439.9752272409</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11575.8597646525</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13537.7669856157</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12730.6615346379</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13991.7187918737</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>12130.8558103576</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10963.9641155335</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11646.4237148805</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11706.2852755619</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>12292.616005173</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13497.0686885696</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13999.4613082209</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14788.3727123433</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11640.9653429078</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>73952.8626956614</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>117653.283815901</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>132286.770695947</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>133763.978411874</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>140567.765073494</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>174230.936413253</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>178264.304358824</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>174134.440374076</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>160075.919483385</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>164114.925073031</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>189445.801585511</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>216505.006047818</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>214495.97234633</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>231885.25613643</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>205901.320808156</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>251367.13764433</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>264759.221570503</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>286395.569455505</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>280617.383448048</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>273011.818186583</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>301891.319060504</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>292661.391156784</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>303007.793460782</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>321924.91451976</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>352828.559305866</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>360972.724252553</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>358331.326015954</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>427191.679971183</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>800413.620698197</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>844315.060481956</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>879232.311458719</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>962706.999825804</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>1182625.28441804</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>1167700.08117373</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>1062778.5189305</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>1028392.65710373</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>1052193.54001609</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>1139157.68972887</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1270212.61280787</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1340261.0376936</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>1432121.60628257</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>1224059.99750177</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1501059.92801209</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1631353.98612729</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.163</t>
+          <t>1872772.96005428</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1862122.29776614</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1725365.89188242</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1950044.24922043</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1818930.3287774</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1837195.48477761</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1932572.13272898</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1967409.30789353</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2022457.31552659</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>2135095.87561636</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>42298.0159705147</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>77400.9231395595</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>75458.7050281388</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>82089.8962967218</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>71228.6435336658</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>106963.997997256</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>105804.456454119</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>99149.1606860875</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>92043.4546578579</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>91587.7017348133</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>108626.359217818</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>117352.613149916</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>116834.069672626</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>154717.535828209</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>124693.8203154</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>137010.592929974</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>176437.695315738</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>166945.59401656</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>169195.175044535</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>144088.759762558</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>157204.170156024</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>149991.144418033</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>149774.80417163</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>148701.813908083</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>158089.776534862</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>143785.724289739</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>150475.276434889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>366747.69319344</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>400934.308307537</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>428996.269989853</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>466609.205005635</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>537337.757042776</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>717230.693236189</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>744110.989270828</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>775786.719826279</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>704167.915145618</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>782240.214946117</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>907242.39157551</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>1030045.73782176</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1020822.80920255</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1050617.02993038</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>861065.614102239</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>921470.125118886</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>974212.781415882</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>1020258.95994566</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>990305.727393516</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>887032.978261422</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>959868.377649722</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>922427.991310053</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>998329.242964741</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>984091.674582243</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>1096596.10451857</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>1095198.72526949</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>1071643.91220365</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>10272.7859242263</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>20905.8337828706</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>20065.4327508485</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>22652.2558942805</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>23170.9808147966</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>35402.1309729452</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>31500.114642451</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>28332.9281884233</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>24846.4455006833</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>26427.6039407023</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>28130.9623127892</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>32348.5520641339</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>30694.3098509145</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>32840.2950756681</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>25237.6983749914</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>33252.0942111352</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>31432.8860343421</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>37736.0470181667</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>36233.5254697901</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>35846.6820623664</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>41027.2936106765</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>34856.2086684058</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>36923.2348653947</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>41011.5046064365</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>45381.3175196466</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>45636.4743316935</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>46419.2494870437</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>109788.36031319</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>91642.8428530539</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>102041.263575982</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>113833.780408583</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>131721.000676593</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>171780.026513143</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>162423.984630916</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>150464.855561742</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>135985.515507309</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>144218.94909325</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>152593.905240096</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>166356.765529642</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>167547.256590668</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>185931.044012587</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>146152.412427171</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>166164.414857585</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>188440.39389851</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>190219.69294796</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>189719.106875074</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>176522.868756647</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>188140.925194628</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>167813.248870675</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>174450.295782906</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>174209.272311196</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>191909.574052968</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>184126.746087259</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>182020.275238616</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>570059.831902909</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>821695.902272237</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>776500.360686816</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>879765.14398571</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>916432.045923399</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1216156.59641475</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>1217193.89827994</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>1136740.28576482</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>986876.504799614</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>1071561.93101325</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>1203627.86690733</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>1314727.12835931</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>1337661.12956891</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>1156506.10944679</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>1119023.4643766</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1317936.54088404</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>1409956.9343896</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>1538442.19248553</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>1632714.31779435</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>1336615.55040812</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>1441501.78984728</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>1379666.35961293</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>1311422.47407593</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>1376038.02465213</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>1432509.17797941</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>1377293.11190565</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>1455681.63619476</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>344514.277062392</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>461329.814551306</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>524227.482612347</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>536085.133739987</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>579184.214421584</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>690870.313934445</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>672650.403628068</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>674879.153929506</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>604785.049979185</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>691460.69393058</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>753895.142834668</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>754497.388316684</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>710788.895657323</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>746087.498591933</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>713750.231630189</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>781699.624611905</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>820022.408635687</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>973325.161968798</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>954923.42316854</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>884473.771005836</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>1023634.71658885</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>1032944.58296572</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>958861.04385044</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>938400.300291051</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1025595.16311292</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1023203.55183819</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1035946.11069176</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>61749.0120455046</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>150445.477970361</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>141555.278085528</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>144672.674051551</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>164874.460461805</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>206302.238475891</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>217289.459152226</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>211416.008903452</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>189806.071826476</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>188165.194678564</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>189035.258970427</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>209545.256993026</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>219630.393304103</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>219190.019326479</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>188660.563161015</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>223441.804764468</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>212806.910860381</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>223408.499937257</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>197652.937261241</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>175534.335481188</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>175956.158590219</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>162694.662351191</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>162283.364173089</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>173551.337736059</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>188826.708856184</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>186431.439366949</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>176761.043688903</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>68255.1316855786</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>127629.019943488</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>126028.218395047</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>139210.397884084</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>160722.364937864</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>190538.351595413</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>210068.770011072</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>205175.293255968</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>185509.335513763</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>194742.744949168</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>208431.357963917</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>214650.520343544</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>210261.08736441</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>226496.506776922</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>191891.364956256</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>221457.197426431</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>232772.45644355</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>232045.436423754</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>227160.407879635</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>229956.58139131</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>261219.728908129</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>258184.794923054</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>273214.480508623</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>301705.675295824</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>319226.015860074</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>330675.365351662</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>322294.337444631</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8.728</t>
+          <t>9820731.91670884</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>7749126.07144752</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>8812929.57327268</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7.779</t>
+          <t>8808042.87886911</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>8.342</t>
+          <t>9437230.95032556</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10.459</t>
+          <t>11819032.7024544</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11.507</t>
+          <t>12977562.4031927</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11.056</t>
+          <t>12462718.0646424</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>10.216</t>
+          <t>11475125.3626947</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10.518</t>
+          <t>11791075.2601386</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11.279</t>
+          <t>12690131.5644228</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>12.059</t>
+          <t>13533681.4217062</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>12.237</t>
+          <t>13778944.4125429</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14535106.4380011</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>13.002</t>
+          <t>14625487.3140413</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>15.024</t>
+          <t>16933077.0282907</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>17537276.2973837</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>17.121</t>
+          <t>19316570.6497139</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>16.042</t>
+          <t>18214315.2139306</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>15.931</t>
+          <t>18224424.4393874</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>18.912</t>
+          <t>21883011.335854</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>20.688</t>
+          <t>23997319.2269399</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>23.157</t>
+          <t>27064353.2154044</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>25.281</t>
+          <t>29581985.3404169</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>26.051</t>
+          <t>30678402.8262158</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>27.692</t>
+          <t>32588301.8866189</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>29.166</t>
+          <t>34341224.4011638</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1570228.145479</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1603600.51657868</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1907794.67729482</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1861165.10576569</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>2048015.57488022</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>2289916.31632019</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2500095.1432129</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2609530.78536285</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2464973.47477027</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>2319640.2360617</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>2760072.50094766</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>3078174.0761454</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>3057858.84033321</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.338</t>
+          <t>3197628.08987601</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3646477.315549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2.873</t>
+          <t>3967699.4214132</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>4192992.43312576</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>4313903.68435448</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>3.153</t>
+          <t>4365511.05198908</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>3.308</t>
+          <t>4596442.72420225</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>3.219</t>
+          <t>4511174.39959203</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>5041333.19413201</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>3.933</t>
+          <t>5540027.58993698</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4.094</t>
+          <t>5784962.89019171</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>5829607.72088853</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>6321015.28985574</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>4.592</t>
+          <t>6532757.68947555</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>39073.4608399087</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>48419.9995887222</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>53156.7653123529</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>57589.211441284</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>62315.5921947168</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>86155.8427624015</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>86034.5961197658</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>75144.5963139262</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>65809.7145380908</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>74741.3045576125</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>89893.7448884293</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>101143.986383149</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>96061.6785677407</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>107748.930163702</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>79676.7280092095</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>75355.0143467799</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>73331.3253762435</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>83933.6265934181</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>90115.1987381898</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>89802.8578199419</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>139028.177267181</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>151210.71038359</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>148287.254230723</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>185796.116499534</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>212305.819215127</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>230653.681033465</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>265244.913836706</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>341938.136605008</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>662845.119919313</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>722763.281738959</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>742390.042011105</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>827015.406279699</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>993810.14027472</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>1018004.08708763</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>983444.148410948</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>817251.503951286</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>951150.968657795</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>1027938.56454156</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>1154471.2980225</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>1116680.60879583</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>1204268.79572171</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>1055393.70950339</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>1238793.73337053</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>1339768.07932861</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>1411638.62498508</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>1359294.86798568</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>1177436.66340236</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>1260954.35746914</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1189726.88270848</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>1184855.48488958</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>1231239.21818013</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1296825.11876309</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>1247497.18536102</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>1253343.44595011</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1813407.03820657</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1576806.96500735</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>1725261.2252146</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1595295.63396204</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1726136.12240754</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>2115713.24452754</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>2199583.87074838</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>2069289.01495371</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1751062.62733231</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>1841558.38811987</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>2100229.21774878</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2087612.83680221</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1970479.11074837</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.992</t>
+          <t>2201405.56010992</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1931996.58952167</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2342855.45470953</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2.279</t>
+          <t>2549510.68695198</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2737052.61156957</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.341</t>
+          <t>2635464.5614244</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1.965</t>
+          <t>2258763.96940193</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2546158.08290328</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2661575.73444064</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2.304</t>
+          <t>2700423.06791629</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.347</t>
+          <t>2774166.05486417</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2.429</t>
+          <t>2879363.16480796</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2908270.73025955</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2.249</t>
+          <t>2692781.51420951</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>538707.715526128</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>553777.493992695</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>652468.508409186</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>570109.929223995</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>639781.232579108</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>869240.992538326</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>871910.948077003</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>894723.457573979</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>757135.294805184</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>927945.712260615</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1032109.01234551</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1101866.23005829</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>1077749.06994524</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>1215819.76622403</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1078792.98981328</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1280850.03733301</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>1504272.67528791</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1585058.53909825</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1624611.12323473</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1632704.29742394</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>2079581.74448986</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>2082211.15741883</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2338416.6970943</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2456932.36351385</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1.922</t>
+          <t>2552377.62040623</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>2537424.98863883</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>2622705.52672176</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>19153.4507504199</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>32508.9988818879</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>44281.5873112619</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>41962.3222928432</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>44979.6532914474</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>52966.2475816172</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>51382.7085957056</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>46963.8623719323</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43850.923542749</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43630.6574344526</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43054.9458160622</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>46451.2091164412</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>45146.7258877728</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>49995.1444357428</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>42710.0081763276</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>47034.3354800476</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>47479.900293164</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>56111.2952512185</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>51679.9172091486</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>50861.6208657478</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>59674.3788115101</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>56313.4041845779</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>62018.1692735127</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>66504.7828291234</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>76091.0100854452</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>76016.6335498025</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>68803.3467885474</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1752.77639047282</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5252.61892441188</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5389.67519707358</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6386.00299174628</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8316.83799605171</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10658.593071021</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10356.1223899027</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10198.0465474157</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9037.34934688567</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11997.5624192795</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13151.7138458428</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13611.0515159267</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12855.6998336006</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>16742.2462635507</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15142.0852277816</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>19144.864281185</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>20777.4363392287</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>23879.904754629</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>28376.7741260895</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>34223.3961080491</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>46301.1922729438</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>47218.8332432346</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>35755.2386291188</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>43083.6580182971</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>38130.4723235839</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>44964.7414098325</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>51360.5610823727</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11337.7098860831</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>21034.0202440076</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>25322.5753580525</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>24743.5590767899</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>29452.8785150195</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>36311.4438049484</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>34070.7201187246</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>32427.5536219817</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>29589.8189591754</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>32108.0198339431</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33680.8890233926</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>36194.0713086499</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>38046.2567676507</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>38165.3187563351</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33585.7538953302</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>31805.4289816668</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>33963.3533403997</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>38320.7235753094</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>34683.2449282078</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>37080.0374306145</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>41615.9642839103</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>38964.6854696464</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>40799.3306985445</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>46212.1269460591</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>49394.1330481624</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>48641.78299371</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>46063.7811023125</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>479720.398585205</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>463504.79937071</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>552275.179753313</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>622816.366321369</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>641572.286255935</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>834100.715444276</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>831564.819582885</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>780173.259858267</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>710475.977835265</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>693751.360378365</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>762006.483905948</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>824927.069022059</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>840500.042186342</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>886362.332832219</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>893534.082069594</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>1051031.91121256</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1138098.73652695</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1313234.07266964</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1356303.27636658</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1409037.09474814</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1816381.43794162</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1557344.9750256</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1494305.12394434</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1693516.69028747</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1823012.20551969</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>1872559.75404425</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1.703</t>
+          <t>2027199.68914797</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2655.00517339637</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3358.50174951866</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3527.43545099793</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3774.80759494585</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5208.0181499822</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8187.56015807014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7210.1039249097</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6060.19127724852</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6228.83295362276</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6199.90369116952</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6064.67937579158</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6886.31182522123</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6983.25132759546</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6992.69328998451</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8097.38094764286</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8104.72795133776</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7140.95635993232</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8299.57326705278</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9853.36888286294</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9664.53017779</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14205.7197331794</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9389.39845285816</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13227.2645876114</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12099.7499112242</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12538.5794769199</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12454.074627824</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12230.2681253184</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>119131.304289781</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>225241.534522107</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>227793.104670567</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>237664.024626717</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>281957.885296066</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>337449.910720499</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>356066.915821084</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>335366.885736515</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>287926.883306015</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>309933.607082702</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>315789.816548241</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>351608.86178732</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>328235.857745767</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>385220.462903223</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>351400.904625271</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>413797.15512123</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>393570.789191942</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>507419.896563101</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>531431.792121376</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>433186.7120604</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>447313.910476114</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>473827.631598019</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>436240.821812058</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>477309.949127087</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>489039.503253122</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>524033.769145962</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>572328.261373401</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>179506.298323774</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>381917.104877238</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>380079.311993087</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>376938.022479124</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>407451.057109217</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>481434.820695671</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>479233.468058739</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>448939.239788632</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>402033.945740578</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>400134.765842071</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>431376.152475054</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>466700.559702577</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>491930.68833418</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>525964.836147816</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>490290.299488174</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>578320.184534057</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>610200.947168412</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>644936.940170695</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>635137.857580071</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>658457.1419836</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>776593.34371066</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>705962.760063553</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>707452.67883364</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>801391.055398204</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>857352.965398523</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>898421.389894472</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>879887.318294538</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>53858.299933092</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>111981.426775587</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>105288.588334946</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>110331.561646843</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>126397.415632591</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>152095.205693625</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>149591.803056609</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>143562.533800988</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>126337.690751241</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>128459.190429168</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>137713.3068102</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>141454.297845776</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>143076.851364108</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>156237.00514866</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>136610.156673714</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>154165.658234339</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>165517.976398679</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>172826.4546974</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>174883.15876229</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>153848.778206589</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>166956.752295189</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>154392.523381454</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>165470.114365072</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>177862.809096873</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>184037.345496838</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>184715.730952591</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>178480.140986414</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>98615.3077027208</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>192068.830469068</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>217942.781565979</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>262209.609444666</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>271915.988593574</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>327388.345813727</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>323309.773853573</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>305567.504476426</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>243699.728520902</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>239955.289698612</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>254669.770079921</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>248991.128135887</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>264878.960546397</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>277825.574909791</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>256462.110822277</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>297006.357195205</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>308682.6044826</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>353385.65279703</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>325930.892799823</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>367372.159354783</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>391655.061527525</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>394858.169710743</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>405718.469765676</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>431156.425999533</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>497984.730014021</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>522590.804728939</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>485418.094756605</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>853623.267298206</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>1120259.88570103</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>1424536.03763024</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>1252100.44094228</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>1375449.89862218</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1790248.9820772</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1911143.1886743</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1573619.15933541</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1539356.74088862</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>1586241.175781</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1601899.09457723</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1827768.78102094</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1833980.06548426</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>2021948.19518732</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1875816.22541765</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>2155146.79437909</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>2478135.14365976</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>2476157.92533795</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.811</t>
+          <t>2610640.35453778</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.849</t>
+          <t>2674215.03996918</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>2503504.89587058</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1865077.46926571</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>2021668.1559872</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>2224041.10104442</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>2496040.29945961</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>1.674</t>
+          <t>2495751.59527638</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1.652</t>
+          <t>2471461.06979628</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>59865.4773833746</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>38412.9791548937</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>54363.5316088376</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52704.6018788137</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52532.7546718274</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>65620.0354923215</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>66579.3474098692</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62124.8987473769</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>57975.4706075823</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>57817.547362605</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62866.1630309541</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>72735.3874722796</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>75309.4808408174</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>85772.7573953338</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>82537.9054816699</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>84528.0783713168</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>92619.0733139964</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>102816.459849393</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>103974.715361883</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>103112.326395203</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>119670.79802673</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>118266.749133904</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>116233.625040004</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>130948.412286923</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>140175.016627635</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>142463.367551579</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>135817.77571583</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11101.7580443013</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>25086.9792489313</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23657.1837849332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22770.979668108</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25230.4392934652</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>30084.5514015483</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30182.5362674138</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>28912.3726272362</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26837.7091066376</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26455.831286663</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30919.8991207114</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35425.4740682006</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>35197.3906594928</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>37036.4219101242</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32193.8034856195</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36885.3369475343</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>40390.6895011497</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>42052.2327994511</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>41197.8474541341</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39809.1431518931</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>42924.0480876268</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>43100.9973659018</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>47706.3941804008</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>50078.7467910405</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>53933.6142356502</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>56316.8691945931</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>49574.6042776208</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>70544.0231923903</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>69114.0550226058</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>72767.6368634095</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>78809.9886007661</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>80737.241669212</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>111331.91920989</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>110091.857551685</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>104574.079479055</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>93035.3217017888</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>97554.735966768</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>108591.874217701</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>118236.293418899</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>118948.732179868</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>124005.536941738</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>109679.468852329</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>122088.868877774</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>142020.545875972</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>154067.794562078</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>150182.371299877</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>147088.75363494</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>158639.330535607</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>139761.399505659</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>138149.218376148</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>135117.839777081</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>140609.152231717</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>139132.837525029</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>143833.96482523</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>314442.182222076</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>627961.450939684</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>642874.346016128</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>665546.918896261</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>784127.901569078</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>932102.954016223</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>911411.980959041</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>1008720.76277969</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>884021.531502075</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>976014.289112067</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>1075069.46033585</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>1172805.87952506</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>1071919.88057997</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1159498.47571678</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>883663.869682968</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>961680.756971697</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>1165927.92653342</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1609932.62070181</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>1360130.29525275</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>1382033.3789358</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>1418316.18150237</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>1427575.9838761</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1478185.88953218</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>1373220.03952234</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>1175241.38812844</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>1277896.66064745</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>1257865.03365172</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>424276.885196284</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>431516.515520334</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>480067.489877926</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>466898.481833599</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>532711.097354966</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>673847.844311259</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>651385.856697027</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>670065.977249113</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>590402.079359885</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>731360.074188279</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>816821.549133869</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>867325.620794456</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>754139.281983696</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>816647.988070798</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>786181.651605462</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>989038.170857583</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>1141855.14140808</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1238791.95467867</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>1316669.9954718</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>1486913.6544806</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>1709221.71636553</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>2412940.65515486</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>1634827.66126587</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>1666915.1583319</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>1638366.96765181</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>1703570.33750651</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>2102959.3379892</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1584018.61458792</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1617014.94952643</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1956127.0338775</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>1828779.56739762</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2299644.51805518</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.366</t>
+          <t>2868969.57273895</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.338</t>
+          <t>2831792.98567542</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.283</t>
+          <t>2766469.63113813</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.034</t>
+          <t>2439473.84385841</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2253848.53740376</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2844025.15642432</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2706746.03719472</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.337</t>
+          <t>2783291.17057733</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.564</t>
+          <t>3066993.90515206</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.174</t>
+          <t>2599542.89026813</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2.501</t>
+          <t>3014584.46712684</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2.704</t>
+          <t>3272937.80851247</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>3165848.87609306</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2.956</t>
+          <t>3583641.38660255</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3105322.2024016</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>3.085</t>
+          <t>3785471.81954771</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>3.265</t>
+          <t>4003842.81083415</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>3.506</t>
+          <t>4337226.44103851</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>4237793.64591009</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>3.666</t>
+          <t>4550929.54574792</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>3.755</t>
+          <t>4675882.63697344</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>3.752</t>
+          <t>4687145.04684685</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>43.349</t>
+          <t>54350274.2827501</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>45.677</t>
+          <t>57209883.8151937</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>51.181</t>
+          <t>64271647.1876827</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>51.473</t>
+          <t>64622574.1065296</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>56.414</t>
+          <t>71023838.1844459</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>68.559</t>
+          <t>86657240.0827002</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70.325</t>
+          <t>88750773.4552537</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>68.945</t>
+          <t>86847033.7418469</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>64.708</t>
+          <t>81173223.2938115</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>66.874</t>
+          <t>83709594.98089</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>73.555</t>
+          <t>92103355.3348949</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>79.902</t>
+          <t>99948801.7679264</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>83.248</t>
+          <t>103975761.651795</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>86.083</t>
+          <t>107515443.752738</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>83.853</t>
+          <t>105157924.510046</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>98.291</t>
+          <t>123532765.103892</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>105.781</t>
+          <t>133083978.216761</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>116.846</t>
+          <t>147268078.882938</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>116.108</t>
+          <t>146363425.745529</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>119.319</t>
+          <t>150601270.332599</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>135.06</t>
+          <t>171285779.629825</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>136.589</t>
+          <t>173305227.25441</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>142.874</t>
+          <t>181224134.969356</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>146.798</t>
+          <t>186509735.397727</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>157.028</t>
+          <t>199761577.622657</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>161.948</t>
+          <t>206167238.989671</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>166.699</t>
+          <t>212326779.862302</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>25746.4200560379</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>50599.3348965838</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>59743.8136359422</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>63121.3193296047</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>62148.9929781847</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>69127.1685661839</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>71838.2653161222</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>66404.8010715321</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>61667.2692033638</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>65119.9472424366</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>71629.5346557574</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>80856.3051305769</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>78840.1170146508</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>82888.0927477338</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>79355.9033819058</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>89045.2625361384</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>90099.9822450945</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>92402.0387046183</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>85441.2054948226</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>83451.1827372859</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>88889.7927737773</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>83248.6832863832</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>102102.029189441</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>129841.68794618</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>114369.931620259</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>112878.776322078</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>101342.502621845</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>98548.4990241234</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>116666.646282927</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>122706.190614831</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>138423.276223697</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>143165.699732649</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>166740.532348138</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>167178.473143987</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>167027.256320981</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>148513.837941159</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>175547.991398322</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>186806.16005038</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>204614.367891379</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>179417.384769188</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>235013.732953696</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>220935.058985151</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>234675.614508356</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>273319.281298694</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>309969.463861483</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>322485.509296433</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>285083.984224829</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>326169.098292514</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>315077.752307791</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>300249.836245428</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>316012.129401812</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>302853.693803766</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>339088.658777609</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>401977.653236952</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>27399.4888362222</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>47108.6087948424</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>51662.0478580044</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>55961.0806617143</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>64593.3639813059</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>70882.3378671841</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>69542.8115825326</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>72958.6670885441</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>74755.5708634611</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>62312.0128889796</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>69022.0511208595</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>76806.7889578065</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>81413.9903583233</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>101947.801672448</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>87209.062372903</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>104133.900933611</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>115264.175464367</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>141725.057060556</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>156199.211369579</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>142122.273997873</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>140757.945030406</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>116857.618509453</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>119141.42417439</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>112140.931961566</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>121250.415525299</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>120211.727059777</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>118322.062419773</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>126846.498792106</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>277183.730892006</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>302092.919871782</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>327337.163660741</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>317672.979302048</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>402398.350716503</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>347562.279266183</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>338095.773523059</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>319675.632107079</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>319891.773779574</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>336846.07055694</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>356299.320318127</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>347428.042686078</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>386627.841203767</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>369539.521875679</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>413506.798144574</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>433646.264082146</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>507232.514874998</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>493521.070329981</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>428804.478643763</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>449350.253164148</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>427179.956646196</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>507595.476222281</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>484730.415561924</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>531421.493496368</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>525393.724763318</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>490864.773975968</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5.993</t>
+          <t>8777613.37645301</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.326</t>
+          <t>6373812.33046589</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>7373810.58530549</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5.452</t>
+          <t>7909043.50954074</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>9260637.83469958</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>11503930.4787587</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8.077</t>
+          <t>11735237.2853562</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8.249</t>
+          <t>11937913.4288277</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>7.906</t>
+          <t>11443590.9495006</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8.188</t>
+          <t>11770612.5199926</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>9.095</t>
+          <t>13080315.017641</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>9.941</t>
+          <t>14273453.6011442</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>10.473</t>
+          <t>15111155.2744513</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>11.374</t>
+          <t>16220670.9190586</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>16241630.9722431</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>13.471</t>
+          <t>19343150.6532079</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>14.098</t>
+          <t>20180111.8596866</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>15.965</t>
+          <t>22950307.6124153</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>15.333</t>
+          <t>22115344.2452168</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>16.612</t>
+          <t>24366172.6772922</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>18.359</t>
+          <t>27416473.9949591</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>17.829</t>
+          <t>26609401.9387145</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>18.502</t>
+          <t>27805862.8609915</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>27574835.4309073</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>18.975</t>
+          <t>28631100.0900447</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19.524</t>
+          <t>29428254.1607994</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>20.184</t>
+          <t>30592915.9279166</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>1277230.85648278</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>1908304.32564622</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>2168468.46880519</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2337357.25699543</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>2442525.9499648</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>2972071.755014</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>3037678.8755211</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2.062</t>
+          <t>2997776.67029165</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>2845214.39152757</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>2841272.95654543</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2.078</t>
+          <t>2995413.23917247</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>3264542.9129461</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>3448304.87422238</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>3871414.10396247</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4019949.46278878</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t>4641132.31304178</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>3.564</t>
+          <t>5123068.13393591</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5765399.52482108</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>3.838</t>
+          <t>5547006.60878013</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>3.645</t>
+          <t>5290451.04452604</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5788860.89312727</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>5857934.72600596</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>5763948.43158691</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5632345.20659469</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>3.607</t>
+          <t>5404162.44334753</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>3.402</t>
+          <t>5098083.89735219</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>3.234</t>
+          <t>4859114.85439294</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>3207298.97960269</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>4346511.80016576</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>4700952.12746885</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.145</t>
+          <t>4763045.27982619</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>5046483.52475292</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.898</t>
+          <t>5878154.77474342</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3.682</t>
+          <t>5555751.51343545</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3.559</t>
+          <t>5270481.06868934</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>5203644.32188804</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>3.453</t>
+          <t>5140575.31645138</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>3.593</t>
+          <t>5344003.42380184</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>3.927</t>
+          <t>5789059.48151095</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>4.233</t>
+          <t>6302253.71408847</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5879439.32476181</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>3.884</t>
+          <t>5727434.4782304</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>4.901</t>
+          <t>7221343.62769774</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>4.697</t>
+          <t>6909451.21006184</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7551792.56588634</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>4.973</t>
+          <t>7328653.77095537</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>5.294</t>
+          <t>7896853.49679931</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>5.107</t>
+          <t>7705780.02704573</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>4.402</t>
+          <t>6690322.43365529</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>6750179.08341689</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>4.897</t>
+          <t>7464315.45164459</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>8596792.73365645</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>5.909</t>
+          <t>9075816.63358758</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>8827759.13639428</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5838313.09703724</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>6241733.5037531</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4.846</t>
+          <t>6946307.51611684</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5.324</t>
+          <t>7583014.87512601</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>5.751</t>
+          <t>8183314.79712206</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7.114</t>
+          <t>10103117.6279483</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7.257</t>
+          <t>10324302.7436554</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>7.118</t>
+          <t>10075981.8673741</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>6.777</t>
+          <t>9544428.37752898</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>6.812</t>
+          <t>9574699.96917848</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>7.448</t>
+          <t>10478097.3208938</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>8.179</t>
+          <t>11507829.9030191</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>8.635</t>
+          <t>12132865.5168169</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>13043920.9154542</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>9.204</t>
+          <t>12917989.7948842</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10.891</t>
+          <t>15367660.2328327</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12.129</t>
+          <t>17191751.2343225</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>18851701.6329939</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>18463292.6508413</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>12.816</t>
+          <t>17922070.8181264</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>14.268</t>
+          <t>20120576.7731025</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>14.214</t>
+          <t>20168609.5659476</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>13.925</t>
+          <t>19877140.6344853</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>19559288.6460513</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>15.001</t>
+          <t>21612630.0156621</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15.701</t>
+          <t>22596432.9616712</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>15.787</t>
+          <t>22738148.2193936</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>597854.352539935</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>487054.92963404</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>586580.008393422</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>627632.923837718</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>704356.442068736</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>933823.982866502</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>1047158.30177874</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>1099509.69176549</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>967071.771201762</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1110147.2536193</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>1250045.83765508</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1460719.47387172</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1625513.93695664</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1950557.39094927</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1892316.46335225</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2230808.3570227</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>2441344.92357823</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>2884287.72505656</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>2838526.24729137</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>2705275.81042281</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>2868531.0732098</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1.839</t>
+          <t>2646089.69970649</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>2805413.63238542</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>1.904</t>
+          <t>2751435.53142434</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1.955</t>
+          <t>2833319.97664156</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>3077875.41377187</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>3052355.06634999</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
